--- a/public/downloads/Anexos/Ejemplo_2_calculo_y_grafico.xlsx
+++ b/public/downloads/Anexos/Ejemplo_2_calculo_y_grafico.xlsx
@@ -3502,13 +3502,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66381CF1-9994-44BD-A814-73ABAAF6FAB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C6575FB-7C92-481C-A921-E1C8C3FCB149}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4056AAC9-63AF-4B38-840B-BFDBEB888BC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2A8092-8909-4DD4-BA5D-F73F72BCD386}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A264CEF-F5FC-4A32-8A3F-26928A7E039E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57D26951-38C1-43CC-8F8D-17F47007DBB3}"/>
 </file>